--- a/Codelist Excel Files and Conversion Templates to XML/grout_inj_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/grout_inj_properties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/Documents/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0716067E-728B-1E46-BC3B-6DFD3C5BB1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1CE4B7-C594-1944-8CB9-39F97F10CFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11720" yWindow="3840" windowWidth="35840" windowHeight="20900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="354">
   <si>
     <t>Start</t>
   </si>
@@ -402,9 +402,6 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>packer pressure</t>
@@ -1447,6 +1444,40 @@
       <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
       <font>
         <color auto="1"/>
       </font>
@@ -1542,40 +1573,6 @@
       </font>
       <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" wrapText="1"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
   <extLst>
@@ -1590,33 +1587,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:E3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H37" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H37" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="A1:H37" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="19">
       <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B423,1,FALSE)),"Not used","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2592,9 +2589,6 @@
       <c r="E27" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="G27" s="11"/>
     </row>
     <row r="28" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2606,10 +2600,10 @@
         <v>34</v>
       </c>
       <c r="C28" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" s="17" t="s">
         <v>123</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>124</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>64</v>
@@ -2628,10 +2622,10 @@
         <v>35</v>
       </c>
       <c r="C29" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" s="17" t="s">
         <v>125</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>126</v>
       </c>
       <c r="E29" s="19" t="s">
         <v>64</v>
@@ -2650,10 +2644,10 @@
         <v>36</v>
       </c>
       <c r="C30" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" s="17" t="s">
         <v>127</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>128</v>
       </c>
       <c r="E30" s="19" t="s">
         <v>64</v>
@@ -2672,16 +2666,16 @@
         <v>37</v>
       </c>
       <c r="C31" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" s="17" t="s">
         <v>129</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>130</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>64</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G31" s="11"/>
     </row>
@@ -2694,16 +2688,16 @@
         <v>38</v>
       </c>
       <c r="C32" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D32" s="17" t="s">
         <v>132</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>133</v>
       </c>
       <c r="E32" s="19" t="s">
         <v>64</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G32" s="11"/>
     </row>
@@ -2716,13 +2710,13 @@
         <v>39</v>
       </c>
       <c r="C33" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="D33" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="E33" s="19" t="s">
         <v>135</v>
-      </c>
-      <c r="E33" s="19" t="s">
-        <v>136</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>65</v>
@@ -2738,10 +2732,10 @@
         <v>40</v>
       </c>
       <c r="C34" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="17" t="s">
         <v>137</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>138</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>64</v>
@@ -2763,13 +2757,13 @@
         <v>41</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>64</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G35" s="11"/>
     </row>
@@ -2785,13 +2779,13 @@
         <v>43</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>64</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G36" s="11"/>
     </row>
@@ -2807,7 +2801,7 @@
         <v>42</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E37" s="21" t="s">
         <v>42</v>
@@ -2822,10 +2816,10 @@
         <v>45</v>
       </c>
       <c r="C38" t="s">
+        <v>143</v>
+      </c>
+      <c r="D38" t="s">
         <v>144</v>
-      </c>
-      <c r="D38" t="s">
-        <v>145</v>
       </c>
       <c r="E38" t="s">
         <v>64</v>
@@ -2839,10 +2833,10 @@
         <v>46</v>
       </c>
       <c r="C39" t="s">
+        <v>145</v>
+      </c>
+      <c r="D39" t="s">
         <v>146</v>
-      </c>
-      <c r="D39" t="s">
-        <v>147</v>
       </c>
       <c r="E39" t="s">
         <v>64</v>
@@ -2856,10 +2850,10 @@
         <v>47</v>
       </c>
       <c r="C40" t="s">
+        <v>147</v>
+      </c>
+      <c r="D40" t="s">
         <v>148</v>
-      </c>
-      <c r="D40" t="s">
-        <v>149</v>
       </c>
       <c r="E40" t="s">
         <v>64</v>
@@ -3778,7 +3772,7 @@
         <v>58</v>
       </c>
       <c r="B1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C1" t="s">
         <v>59</v>
@@ -3786,64 +3780,64 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" t="s">
         <v>151</v>
-      </c>
-      <c r="C2" t="s">
-        <v>152</v>
       </c>
       <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" t="s">
         <v>153</v>
-      </c>
-      <c r="C3" t="s">
-        <v>154</v>
       </c>
       <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B4" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" t="s">
         <v>155</v>
-      </c>
-      <c r="C4" t="s">
-        <v>156</v>
       </c>
       <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B5" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" t="s">
         <v>157</v>
-      </c>
-      <c r="C5" t="s">
-        <v>158</v>
       </c>
       <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" t="s">
         <v>159</v>
-      </c>
-      <c r="C6" t="s">
-        <v>160</v>
       </c>
       <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" t="s">
         <v>161</v>
-      </c>
-      <c r="C7" t="s">
-        <v>162</v>
       </c>
       <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" t="s">
         <v>163</v>
-      </c>
-      <c r="C8" t="s">
-        <v>164</v>
       </c>
       <c r="D8" s="7"/>
     </row>
@@ -3852,167 +3846,167 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" t="s">
         <v>166</v>
-      </c>
-      <c r="C10" t="s">
-        <v>167</v>
       </c>
       <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C11" t="s">
         <v>168</v>
-      </c>
-      <c r="C11" t="s">
-        <v>169</v>
       </c>
       <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" t="s">
         <v>170</v>
-      </c>
-      <c r="C12" t="s">
-        <v>171</v>
       </c>
       <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C14" t="s">
         <v>173</v>
-      </c>
-      <c r="C14" t="s">
-        <v>174</v>
       </c>
       <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" t="s">
         <v>175</v>
-      </c>
-      <c r="C15" t="s">
-        <v>176</v>
       </c>
       <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" t="s">
         <v>177</v>
-      </c>
-      <c r="C16" t="s">
-        <v>178</v>
       </c>
       <c r="D16" s="7"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" t="s">
         <v>179</v>
-      </c>
-      <c r="C17" t="s">
-        <v>180</v>
       </c>
       <c r="D17" s="7"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="9"/>
       <c r="C18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D18" s="7"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D19" s="7"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C20" t="s">
         <v>183</v>
-      </c>
-      <c r="C20" t="s">
-        <v>184</v>
       </c>
       <c r="D20" s="7"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" t="s">
         <v>185</v>
-      </c>
-      <c r="C21" t="s">
-        <v>186</v>
       </c>
       <c r="D21" s="7"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
+        <v>186</v>
+      </c>
+      <c r="C22" t="s">
         <v>187</v>
-      </c>
-      <c r="C22" t="s">
-        <v>188</v>
       </c>
       <c r="D22" s="7"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" t="s">
         <v>189</v>
-      </c>
-      <c r="C23" t="s">
-        <v>190</v>
       </c>
       <c r="D23" s="7"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
+        <v>190</v>
+      </c>
+      <c r="C24" t="s">
         <v>191</v>
-      </c>
-      <c r="C24" t="s">
-        <v>192</v>
       </c>
       <c r="D24" s="7"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
+        <v>192</v>
+      </c>
+      <c r="C25" t="s">
         <v>193</v>
-      </c>
-      <c r="C25" t="s">
-        <v>194</v>
       </c>
       <c r="D25" s="7"/>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" t="s">
         <v>195</v>
-      </c>
-      <c r="C26" t="s">
-        <v>196</v>
       </c>
       <c r="D26" s="7"/>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
+        <v>196</v>
+      </c>
+      <c r="C27" t="s">
         <v>197</v>
-      </c>
-      <c r="C27" t="s">
-        <v>198</v>
       </c>
       <c r="D27" s="7"/>
     </row>
@@ -4021,13 +4015,13 @@
         <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D28" s="7"/>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D29" s="7"/>
     </row>
@@ -4036,22 +4030,22 @@
         <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D30" s="7"/>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" t="s">
         <v>202</v>
-      </c>
-      <c r="C31" t="s">
-        <v>203</v>
       </c>
       <c r="D31" s="7"/>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C32" t="s">
         <v>65</v>
@@ -4060,253 +4054,253 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
+        <v>204</v>
+      </c>
+      <c r="C33" t="s">
         <v>205</v>
-      </c>
-      <c r="C33" t="s">
-        <v>206</v>
       </c>
       <c r="D33" s="7"/>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
+        <v>206</v>
+      </c>
+      <c r="C34" t="s">
         <v>207</v>
-      </c>
-      <c r="C34" t="s">
-        <v>208</v>
       </c>
       <c r="D34" s="7"/>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
+        <v>208</v>
+      </c>
+      <c r="C35" t="s">
         <v>209</v>
-      </c>
-      <c r="C35" t="s">
-        <v>210</v>
       </c>
       <c r="D35" s="7"/>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C36" t="s">
         <v>211</v>
-      </c>
-      <c r="C36" t="s">
-        <v>212</v>
       </c>
       <c r="D36" s="7"/>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C37" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D37" s="7"/>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C38" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D38" s="7"/>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C39" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D39" s="7"/>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C40" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D40" s="7"/>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C41" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D41" s="7"/>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C42" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D42" s="7"/>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C43" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D43" s="7"/>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C44" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D44" s="7"/>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C45" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D45" s="7"/>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D46" s="7"/>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C47" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D47" s="7"/>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C48" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D48" s="7"/>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C49" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D49" s="7"/>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C50" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D50" s="7"/>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D51" s="7"/>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C52" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D52" s="7"/>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C53" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D53" s="7"/>
     </row>
     <row r="54" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C54" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D54" s="7"/>
     </row>
     <row r="55" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C55" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D55" s="7"/>
     </row>
     <row r="56" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C56" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D56" s="7"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C57" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D57" s="7"/>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C58" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D58" s="7"/>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D59" s="7"/>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C60" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D60" s="7"/>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C61" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D61" s="7"/>
     </row>
     <row r="62" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C62" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D62" s="7"/>
     </row>
     <row r="63" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D63" s="7"/>
     </row>
     <row r="64" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C64" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D64" s="7"/>
     </row>
     <row r="65" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C65" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D65" s="7"/>
     </row>
     <row r="66" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C66" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D66" s="7"/>
     </row>
     <row r="67" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C67" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D67" s="7"/>
     </row>
     <row r="68" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C68" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D68" s="7"/>
     </row>
     <row r="69" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C69" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D69" s="7"/>
     </row>
     <row r="70" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C70" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D70" s="7"/>
     </row>
     <row r="71" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C71" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D71" s="7"/>
     </row>
     <row r="72" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C72" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D72" s="7"/>
     </row>
@@ -4318,25 +4312,25 @@
     </row>
     <row r="74" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C74" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D74" s="7"/>
     </row>
     <row r="75" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C75" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D75" s="7"/>
     </row>
     <row r="76" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C76" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D76" s="7"/>
     </row>
     <row r="77" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C77" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D77" s="7"/>
     </row>
@@ -4348,289 +4342,289 @@
     </row>
     <row r="79" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C79" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D79" s="7"/>
     </row>
     <row r="80" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C80" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D80" s="7"/>
     </row>
     <row r="81" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C81" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D81" s="7"/>
     </row>
     <row r="82" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C82" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D82" s="7"/>
     </row>
     <row r="83" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C83" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D83" s="7"/>
     </row>
     <row r="84" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C84" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D84" s="7"/>
     </row>
     <row r="85" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C85" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D85" s="7"/>
     </row>
     <row r="86" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C86" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D86" s="7"/>
     </row>
     <row r="87" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C87" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D87" s="7"/>
     </row>
     <row r="88" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C88" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D88" s="7"/>
     </row>
     <row r="89" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C89" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D89" s="7"/>
     </row>
     <row r="90" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C90" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D90" s="7"/>
     </row>
     <row r="91" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C91" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D91" s="7"/>
     </row>
     <row r="92" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C92" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D92" s="7"/>
     </row>
     <row r="93" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C93" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D93" s="7"/>
     </row>
     <row r="94" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C94" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D94" s="7"/>
     </row>
     <row r="95" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C95" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D95" s="7"/>
     </row>
     <row r="96" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C96" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D96" s="7"/>
     </row>
     <row r="97" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C97" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D97" s="7"/>
     </row>
     <row r="98" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C98" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D98" s="7"/>
     </row>
     <row r="99" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C99" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D99" s="7"/>
     </row>
     <row r="100" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C100" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D100" s="7"/>
     </row>
     <row r="101" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C101" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D101" s="7"/>
     </row>
     <row r="102" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C102" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D102" s="7"/>
     </row>
     <row r="103" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C103" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D103" s="7"/>
     </row>
     <row r="104" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C104" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D104" s="7"/>
     </row>
     <row r="105" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C105" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D105" s="7"/>
     </row>
     <row r="106" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C106" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D106" s="7"/>
     </row>
     <row r="107" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C107" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D107" s="7"/>
     </row>
     <row r="108" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C108" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D108" s="7"/>
     </row>
     <row r="109" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C109" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D109" s="7"/>
     </row>
     <row r="110" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C110" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D110" s="7"/>
     </row>
     <row r="111" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C111" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D111" s="7"/>
     </row>
     <row r="112" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C112" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D112" s="7"/>
     </row>
     <row r="113" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C113" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D113" s="7"/>
     </row>
     <row r="114" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C114" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D114" s="7"/>
     </row>
     <row r="115" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C115" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D115" s="7"/>
     </row>
     <row r="116" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C116" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D116" s="7"/>
     </row>
     <row r="117" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C117" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D117" s="7"/>
     </row>
     <row r="118" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C118" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D118" s="7"/>
     </row>
     <row r="119" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C119" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D119" s="7"/>
     </row>
     <row r="120" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C120" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D120" s="7"/>
     </row>
     <row r="121" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C121" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D121" s="7"/>
     </row>
     <row r="122" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C122" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D122" s="7"/>
     </row>
     <row r="123" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D123" s="7"/>
     </row>
     <row r="124" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C124" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D124" s="7"/>
     </row>
     <row r="125" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C125" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D125" s="7"/>
     </row>
     <row r="126" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C126" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D126" s="7"/>
     </row>
@@ -4642,199 +4636,199 @@
     </row>
     <row r="128" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C128" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D128" s="7"/>
     </row>
     <row r="129" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C129" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D129" s="7"/>
     </row>
     <row r="130" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C130" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D130" s="7"/>
     </row>
     <row r="131" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C131" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D131" s="7"/>
     </row>
     <row r="132" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C132" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D132" s="7"/>
     </row>
     <row r="133" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C133" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D133" s="7"/>
     </row>
     <row r="134" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C134" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D134" s="7"/>
     </row>
     <row r="135" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D135" s="7"/>
     </row>
     <row r="136" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C136" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D136" s="7"/>
     </row>
     <row r="137" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C137" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D137" s="7"/>
     </row>
     <row r="138" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C138" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D138" s="7"/>
     </row>
     <row r="139" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C139" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D139" s="7"/>
     </row>
     <row r="140" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C140" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D140" s="7"/>
     </row>
     <row r="141" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C141" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D141" s="7"/>
     </row>
     <row r="142" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C142" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D142" s="7"/>
     </row>
     <row r="143" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C143" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D143" s="7"/>
     </row>
     <row r="144" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C144" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D144" s="7"/>
     </row>
     <row r="145" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C145" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D145" s="7"/>
     </row>
     <row r="146" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C146" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D146" s="7"/>
     </row>
     <row r="147" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C147" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D147" s="7"/>
     </row>
     <row r="148" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C148" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D148" s="7"/>
     </row>
     <row r="149" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C149" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D149" s="7"/>
     </row>
     <row r="150" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C150" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D150" s="7"/>
     </row>
     <row r="151" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C151" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D151" s="7"/>
     </row>
     <row r="152" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C152" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D152" s="7"/>
     </row>
     <row r="153" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C153" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D153" s="7"/>
     </row>
     <row r="154" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C154" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D154" s="7"/>
     </row>
     <row r="155" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C155" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D155" s="7"/>
     </row>
     <row r="156" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C156" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D156" s="7"/>
     </row>
     <row r="157" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C157" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D157" s="7"/>
     </row>
     <row r="158" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C158" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D158" s="7"/>
     </row>
     <row r="159" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C159" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D159" s="7"/>
     </row>
     <row r="160" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C160" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D160" s="7"/>
     </row>
@@ -4846,7 +4840,7 @@
     </row>
     <row r="162" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C162" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D162" s="7"/>
     </row>
@@ -4858,37 +4852,37 @@
     </row>
     <row r="164" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C164" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D164" s="7"/>
     </row>
     <row r="165" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C165" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D165" s="7"/>
     </row>
     <row r="166" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C166" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D166" s="7"/>
     </row>
     <row r="167" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C167" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D167" s="7"/>
     </row>
     <row r="168" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C168" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D168" s="7"/>
     </row>
     <row r="169" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C169" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D169" s="7"/>
     </row>
@@ -4900,37 +4894,37 @@
     </row>
     <row r="171" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C171" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D171" s="7"/>
     </row>
     <row r="172" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C172" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D172" s="7"/>
     </row>
     <row r="173" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C173" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D173" s="7"/>
     </row>
     <row r="174" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C174" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D174" s="7"/>
     </row>
     <row r="175" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C175" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D175" s="7"/>
     </row>
     <row r="176" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C176" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D176" s="7"/>
     </row>
@@ -4942,61 +4936,61 @@
     </row>
     <row r="178" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C178" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D178" s="7"/>
     </row>
     <row r="179" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C179" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D179" s="7"/>
     </row>
     <row r="180" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C180" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D180" s="7"/>
     </row>
     <row r="181" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C181" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D181" s="7"/>
     </row>
     <row r="182" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C182" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D182" s="7"/>
     </row>
     <row r="183" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C183" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D183" s="7"/>
     </row>
     <row r="184" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C184" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D184" s="7"/>
     </row>
     <row r="185" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C185" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D185" s="7"/>
     </row>
     <row r="186" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C186" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D186" s="8"/>
     </row>
     <row r="187" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C187" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D187" s="8"/>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/grout_inj_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/grout_inj_properties.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11720" yWindow="3840" windowWidth="35840" windowHeight="20900" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DictionaryName" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Definitions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AssociatedElements" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AlternateNames" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Lists" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DictionaryName" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssociatedElements" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlternateNames" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2287,7 +2287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -3505,6 +3505,669 @@
       <c r="D58" s="3" t="inlineStr">
         <is>
           <t>ancestor::diggs:constructionActivity//diggs:RIInstallationRecord</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>apparent_lugeon_value</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>column_pressure</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>crowd_pressure</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>drilling_index</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>drilling_speed</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>effective_pressure</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>elapsed_time</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>fluid_1_flow</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>fluid_1_pressure</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>fluid_1_temperature</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>fluid_2_flow</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>fluid_2_pressure</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>fluid_2_temperature</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>gauge_pressure</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>grout_flow</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>grout_pressure</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>grout_specific_gravity</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>grout_temperature</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>grout_volume</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>header_pressure</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>injection_pressure</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>line_loss</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>micro_motion_flow</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>micro_motion_volume</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>packer_pressure</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>pull_speed</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>rotary_pressure</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>rotation_speed</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>specific_energy</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>stroke_count</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>thrust</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>torque</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>volume_overconsumption</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>grout_level</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>grout_return_volume</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>//diggs:recordingParameter</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ConstructionActivitySpecification</t>
         </is>
       </c>
     </row>
